--- a/ALL/A1-Pinterest_01-out/START.xlsx
+++ b/ALL/A1-Pinterest_01-out/START.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="40960" windowHeight="22320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Titles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Titles" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,13 +412,233 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:P21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>used_at</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>used_project</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Easy High Protein Chicken Bowl You’ll Love</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:53:15</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A1-Pinterest_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20-Minute High Protein Chicken Dinner</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:53:15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A1-Pinterest_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Healthy Chicken Bowl Better Than Takeout</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:53:15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A1-Pinterest_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Quick High Protein Chicken Meal Prep</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:53:15</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A1-Pinterest_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Easy Chicken and Rice High Protein Recipe</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:53:15</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A1-Pinterest_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Wrap for Busy Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Simple Chicken Bowl for Weight Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Creamy High Protein Chicken Skillet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Spicy Chicken Bowl High Protein Style</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Healthy Chicken Dinner Under 30 Minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Lunch Ideas Easy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chicken Meal Prep Bowls for the Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Alfredo (Healthy Version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Easy Chicken Burrito Bowl High Protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Caesar Salad</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Quick Chicken Wrap for Lunch High Protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Easy Chicken Dinner Ideas Healthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Stir Fry Fast &amp; Easy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Simple Chicken Bowl with Rice Healthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>High Protein Chicken Pasta Easy Recipe</t>
         </is>
       </c>
     </row>

--- a/ALL/A1-Pinterest_01-out/START.xlsx
+++ b/ALL/A1-Pinterest_01-out/START.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="40960" windowHeight="22320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="40960" windowHeight="22260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Titles" sheetId="1" state="visible" r:id="rId1"/>
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-21 00:53:15</t>
+          <t>2026-05-23 16:47:58</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-21 00:53:15</t>
+          <t>2026-05-23 16:47:58</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-05-21 00:53:15</t>
+          <t>2026-05-23 16:47:58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-05-21 00:53:15</t>
+          <t>2026-05-23 16:47:58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-05-21 00:53:15</t>
+          <t>2026-05-23 16:47:58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -543,6 +543,19 @@
           <t>High Protein Chicken Wrap for Busy Days</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-05-23 16:47:58</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A1-Pinterest_01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -550,6 +563,19 @@
           <t>Simple Chicken Bowl for Weight Loss</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-05-23 16:47:58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A1-Pinterest_01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -557,6 +583,19 @@
           <t>Creamy High Protein Chicken Skillet</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-05-23 16:47:58</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A1-Pinterest_01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -564,6 +603,19 @@
           <t>Spicy Chicken Bowl High Protein Style</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-05-23 16:47:58</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A1-Pinterest_01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -571,74 +623,17 @@
           <t>Healthy Chicken Dinner Under 30 Minutes</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>High Protein Chicken Lunch Ideas Easy</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Chicken Meal Prep Bowls for the Week</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>High Protein Chicken Alfredo (Healthy Version)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Easy Chicken Burrito Bowl High Protein</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>High Protein Chicken Caesar Salad</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Quick Chicken Wrap for Lunch High Protein</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Easy Chicken Dinner Ideas Healthy</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>High Protein Chicken Stir Fry Fast &amp; Easy</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Simple Chicken Bowl with Rice Healthy</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>High Protein Chicken Pasta Easy Recipe</t>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-05-23 16:47:58</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A1-Pinterest_01</t>
         </is>
       </c>
     </row>
